--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.57238</v>
+        <v>16.79876</v>
       </c>
       <c r="D2" t="n">
-        <v>16.91484</v>
+        <v>16.61581</v>
       </c>
       <c r="E2" t="n">
-        <v>16.74937</v>
+        <v>16.65128</v>
       </c>
       <c r="F2" t="n">
-        <v>42.76657</v>
+        <v>42.71634</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05092</v>
+        <v>0.05114</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80076</v>
+        <v>1.84725</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.91797</v>
+        <v>16.84624</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4202</v>
+        <v>16.72681</v>
       </c>
       <c r="E3" t="n">
-        <v>16.66884</v>
+        <v>16.79409</v>
       </c>
       <c r="F3" t="n">
-        <v>43.54639</v>
+        <v>42.71464</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0504</v>
+        <v>0.05133</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81937</v>
+        <v>1.81988</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65716</v>
+        <v>16.91085</v>
       </c>
       <c r="D4" t="n">
-        <v>16.51155</v>
+        <v>16.81722</v>
       </c>
       <c r="E4" t="n">
-        <v>16.98746</v>
+        <v>16.8881</v>
       </c>
       <c r="F4" t="n">
-        <v>43.42829</v>
+        <v>41.78155</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0506</v>
+        <v>0.05011</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84288</v>
+        <v>1.81584</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.51571</v>
+        <v>16.59102</v>
       </c>
       <c r="D6" t="n">
-        <v>16.18417</v>
+        <v>15.6381</v>
       </c>
       <c r="E6" t="n">
-        <v>16.34853</v>
+        <v>16.33094</v>
       </c>
       <c r="F6" t="n">
-        <v>21.8667</v>
+        <v>21.75962</v>
       </c>
       <c r="G6" t="n">
-        <v>34.572</v>
+        <v>34.2954</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.93309</v>
+        <v>16.62377</v>
       </c>
       <c r="D7" t="n">
-        <v>16.03437</v>
+        <v>16.08779</v>
       </c>
       <c r="E7" t="n">
-        <v>16.52283</v>
+        <v>16.47641</v>
       </c>
       <c r="F7" t="n">
-        <v>21.88321</v>
+        <v>22.00694</v>
       </c>
       <c r="G7" t="n">
-        <v>34.37512</v>
+        <v>34.71267</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.93885</v>
+        <v>16.86313</v>
       </c>
       <c r="D8" t="n">
-        <v>15.97453</v>
+        <v>16.29989</v>
       </c>
       <c r="E8" t="n">
-        <v>16.48116</v>
+        <v>16.60278</v>
       </c>
       <c r="F8" t="n">
-        <v>22.16972</v>
+        <v>22.09604</v>
       </c>
       <c r="G8" t="n">
-        <v>34.44983</v>
+        <v>33.43304</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.59688</v>
+        <v>0.6037400000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10234</v>
+        <v>1.12091</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60528</v>
+        <v>0.60538</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10607</v>
+        <v>1.11736</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59385</v>
+        <v>0.60804</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10889</v>
+        <v>1.10193</v>
       </c>
     </row>
   </sheetData>
